--- a/Книга1.xlsx
+++ b/Книга1.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr codeName="ЭтаКнига" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Мои документы\JavaScript\Sonata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7844F5D-FE1D-41C9-805B-EF3BB228DD5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F52B6B5B-7FF9-47B8-AECD-A97D1B8A0ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{7E13A5E9-D6E6-4C53-8805-533BEED830C4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7E13A5E9-D6E6-4C53-8805-533BEED830C4}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -81,16 +81,16 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF303243"/>
+      <color rgb="FF48858B"/>
+      <color rgb="FFA2EAFB"/>
+      <color rgb="FF68217A"/>
+      <color rgb="FFB766D8"/>
+      <color rgb="FFB64AD2"/>
+      <color rgb="FFA237BE"/>
       <color rgb="FF3673A5"/>
       <color rgb="FF83CD29"/>
       <color rgb="FFFF3E00"/>
-      <color rgb="FFFF8C01"/>
-      <color rgb="FFD6BA32"/>
-      <color rgb="FF131313"/>
-      <color rgb="FF4C749F"/>
-      <color rgb="FF46962A"/>
-      <color rgb="FF629A1E"/>
-      <color rgb="FFFFDA3E"/>
     </mruColors>
   </colors>
   <extLst>
@@ -108,16 +108,169 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>356153</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>65077</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>435219</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>109904</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>356153</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>157370</xdr:rowOff>
+      <xdr:colOff>176447</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>161193</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1080" name="Прямоугольник: скругленные верхние углы 1079">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B25B70EB-60FC-418D-A900-C715146B460C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000">
+          <a:off x="2582007" y="1443404"/>
+          <a:ext cx="3785690" cy="2791558"/>
+        </a:xfrm>
+        <a:prstGeom prst="round2SameRect">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 3281"/>
+            <a:gd name="adj2" fmla="val 0"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="303243"/>
+        </a:solidFill>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="48858B"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="ru-RU" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>435219</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>174535</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>123300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1079" name="Прямоугольник: скругленные верхние углы 1078">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4F1ED99-DE14-4DE4-A3AD-A12CF2B59E39}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2582007" y="762000"/>
+          <a:ext cx="3783778" cy="694800"/>
+        </a:xfrm>
+        <a:prstGeom prst="round2SameRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="303243"/>
+        </a:solidFill>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="48858B"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="ru-RU" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>93956</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>182214</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>93956</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>77445</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -132,13 +285,13 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="6485283" y="3113077"/>
-          <a:ext cx="0" cy="1806793"/>
+          <a:off x="3427706" y="2468214"/>
+          <a:ext cx="0" cy="540000"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
         </a:prstGeom>
-        <a:ln w="76200">
+        <a:ln w="57150">
           <a:solidFill>
             <a:srgbClr val="FF3E00"/>
           </a:solidFill>
@@ -162,25 +315,305 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>578071</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>36739</xdr:rowOff>
+      <xdr:colOff>819206</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>67297</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>580977</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>140239</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>819206</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>35797</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="34" name="Прямая со стрелкой 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DFB7562-3697-42F3-A40A-5E5AA327CC82}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="5537744" y="2617066"/>
+          <a:ext cx="0" cy="540000"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="57150">
+          <a:solidFill>
+            <a:srgbClr val="83CD29"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>410138</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>185943</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>410138</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>153371</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="37" name="Прямая со стрелкой 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3F9774A-0CEB-4F4A-90A7-C876476925AD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3135753" y="3878712"/>
+          <a:ext cx="0" cy="538928"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="57150">
+          <a:solidFill>
+            <a:srgbClr val="83CD29"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>415439</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>179398</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>415439</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>147898</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="38" name="Прямая со стрелкой 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC4A1971-5F9E-4171-929F-5C9DBF043AB6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="3749189" y="4062667"/>
+          <a:ext cx="0" cy="540000"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="57150">
+          <a:solidFill>
+            <a:srgbClr val="3673A5"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>426241</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>172909</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>426241</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>141409</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="40" name="Прямая со стрелкой 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF317063-4C2B-4C87-A9A9-88BF7B9A27CD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="5144779" y="4056178"/>
+          <a:ext cx="0" cy="540000"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="57150">
+          <a:solidFill>
+            <a:srgbClr val="68217A"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>262375</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>183967</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>262375</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>151395</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="43" name="Прямая со стрелкой 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FBE377A9-9A0F-4BAD-B496-A73D2F6F36E4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="5808856" y="3876736"/>
+          <a:ext cx="0" cy="538928"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="57150">
+          <a:solidFill>
+            <a:srgbClr val="83CD29"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>75772</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>173166</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>600076</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>55963</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="6" name="Группа 5">
+        <xdr:cNvPr id="60" name="Группа 59">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15E44BC6-AFCD-8E5D-C8C4-EA9FFFBB94BB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80281F7A-6016-4BE2-83C3-C7AAD5D27335}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -188,18 +621,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5476642" y="1370239"/>
-          <a:ext cx="6738442" cy="1818000"/>
+          <a:off x="2801387" y="1697166"/>
+          <a:ext cx="3345170" cy="908566"/>
           <a:chOff x="1950692" y="1247775"/>
           <a:chExt cx="6682313" cy="1818000"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="2" name="Прямоугольник: скругленные углы 1">
+          <xdr:cNvPr id="61" name="Прямоугольник: скругленные углы 60">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{737A1A86-3C2C-5150-84A1-BEEF018B299E}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A11E7770-3640-1972-ED55-7DA63546AA15}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -252,10 +685,10 @@
       </xdr:sp>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="5" name="Рисунок 4" descr="Svelte.js — An Introduction to the Compiler as a Framework | by Thibault  Goudouneix | Better Programming">
+          <xdr:cNvPr id="62" name="Рисунок 61" descr="Svelte.js — An Introduction to the Compiler as a Framework | by Thibault  Goudouneix | Better Programming">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BC98FA7-2B4E-4373-827D-3C740C843905}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E315527-ECEE-2A41-6452-01A5846B5C0F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -299,81 +732,25 @@
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>16565</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>29308</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>149087</xdr:rowOff>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>16565</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>51287</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="34" name="Прямая со стрелкой 33">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DFB7562-3697-42F3-A40A-5E5AA327CC82}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1" flipV="1">
-          <a:off x="11049000" y="3197087"/>
-          <a:ext cx="0" cy="1807200"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="76200">
-          <a:solidFill>
-            <a:srgbClr val="83CD29"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>606566</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>14550</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>146644</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>143550</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>624548</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>159264</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="21" name="Группа 20">
+        <xdr:cNvPr id="1026" name="Группа 1025">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1654FC09-A20F-46C0-9D07-AC51EAE8D34C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D363DB9-58AC-40F2-8351-B439933E77D2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -381,18 +758,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5505137" y="4967550"/>
-          <a:ext cx="6887936" cy="2034000"/>
+          <a:off x="2754923" y="3026019"/>
+          <a:ext cx="3416106" cy="1016514"/>
           <a:chOff x="14340254" y="5337664"/>
           <a:chExt cx="6858000" cy="2034000"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="17" name="Прямоугольник: скругленные углы 16">
+          <xdr:cNvPr id="1028" name="Прямоугольник: скругленные углы 1027">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9859A790-204E-4C7A-9D3F-05FC2B9AE1CC}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BE30C42-8CCA-8165-364A-D873A67D7544}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -444,10 +821,10 @@
       </xdr:sp>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="20" name="Рисунок 19">
+          <xdr:cNvPr id="1029" name="Рисунок 1028">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4FFCB31-FD44-4E75-90AB-102E37093027}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{241753B0-945C-0E99-D53B-B64B631D1D86}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -456,7 +833,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
             <a:extLst>
               <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
                 <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -491,193 +868,25 @@
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>521805</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>149086</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>29308</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>168519</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>521805</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>16565</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="37" name="Прямая со стрелкой 36">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3F9774A-0CEB-4F4A-90A7-C876476925AD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="6038022" y="7007086"/>
-          <a:ext cx="0" cy="1581979"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="76200">
-          <a:solidFill>
-            <a:srgbClr val="83CD29"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>114301</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>147431</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>114301</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>49631</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="38" name="Прямая со стрелкой 37">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC4A1971-5F9E-4171-929F-5C9DBF043AB6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1" flipV="1">
-          <a:off x="6856344" y="7005431"/>
-          <a:ext cx="0" cy="1807200"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="76200">
-          <a:solidFill>
-            <a:srgbClr val="3673A5"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>256997</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>162340</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>256997</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>64540</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="40" name="Прямая со стрелкой 39">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF317063-4C2B-4C87-A9A9-88BF7B9A27CD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1" flipV="1">
-          <a:off x="10676519" y="7020340"/>
-          <a:ext cx="0" cy="1807200"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="76200">
-          <a:solidFill>
-            <a:srgbClr val="002060"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>349702</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>39460</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>253703</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>145060</xdr:rowOff>
+      <xdr:colOff>115184</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>30066</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="30" name="Группа 29">
+        <xdr:cNvPr id="1051" name="Группа 1050">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81D4555C-F4A9-431F-F183-B491A1FA7912}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21369785-12FB-4264-ADD4-0D1501F75497}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -685,18 +894,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4635952" y="8611960"/>
-          <a:ext cx="2965608" cy="3153600"/>
+          <a:off x="2754923" y="4432788"/>
+          <a:ext cx="1470665" cy="1576047"/>
           <a:chOff x="7734300" y="4371975"/>
           <a:chExt cx="2952000" cy="3153600"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="25" name="Прямоугольник: скругленные углы 24">
+          <xdr:cNvPr id="1052" name="Прямоугольник: скругленные углы 1051">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED5998E5-1D4B-4765-8539-BA2E9A1872B0}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5EAAF679-FCD7-7C28-B82B-E82756D55B5D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -746,10 +955,10 @@
       </xdr:sp>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="29" name="Рисунок 28">
+          <xdr:cNvPr id="1053" name="Рисунок 1052">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06BF0856-ADBE-4E5F-8DE8-9AB8C0D58ED8}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DDC236E-CB87-BE9B-D89E-4030D2C58237}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -776,81 +985,25 @@
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>53009</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>135833</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>47894</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>168519</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>53009</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>3312</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="43" name="Прямая со стрелкой 42">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FBE377A9-9A0F-4BAD-B496-A73D2F6F36E4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="11698357" y="6993833"/>
-          <a:ext cx="0" cy="1581979"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="76200">
-          <a:solidFill>
-            <a:srgbClr val="83CD29"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>217892</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>52004</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>586745</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>13604</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>616975</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>30066</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="24" name="Группа 23">
+        <xdr:cNvPr id="1054" name="Группа 1053">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ABF77E67-D1FD-2D9A-373B-203C818866E0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88DB10F5-31EC-42BD-9173-B76793EF7CD5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -858,18 +1011,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="10015035" y="8624504"/>
-          <a:ext cx="2818139" cy="3009600"/>
-          <a:chOff x="9982200" y="5295900"/>
-          <a:chExt cx="2806662" cy="3009600"/>
+          <a:off x="4766432" y="4432788"/>
+          <a:ext cx="1397024" cy="1576047"/>
+          <a:chOff x="20206607" y="4191000"/>
+          <a:chExt cx="2817548" cy="3153600"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="22" name="Прямоугольник: скругленные углы 21">
+          <xdr:cNvPr id="1055" name="Прямоугольник: скругленные углы 1054">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CCD165B-C198-4559-B54D-D3BA0879F769}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F797F0B-53BD-2786-CCB3-0374D860DF6B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -877,18 +1030,18 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="9982200" y="5295900"/>
-            <a:ext cx="2806662" cy="3009600"/>
+            <a:off x="20206607" y="4191000"/>
+            <a:ext cx="2817548" cy="3153600"/>
           </a:xfrm>
           <a:prstGeom prst="roundRect">
             <a:avLst/>
           </a:prstGeom>
           <a:solidFill>
-            <a:srgbClr val="4C749F"/>
+            <a:srgbClr val="B766D8"/>
           </a:solidFill>
           <a:ln w="38100">
             <a:solidFill>
-              <a:srgbClr val="002060"/>
+              <a:srgbClr val="68217A"/>
             </a:solidFill>
           </a:ln>
         </xdr:spPr>
@@ -919,51 +1072,78 @@
       </xdr:sp>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="23" name="Рисунок 22">
+          <xdr:cNvPr id="1056" name="Рисунок 1055">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{930E0352-1C5C-4621-ADFD-B1210FCB411F}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20B3F815-3C03-B060-72A2-EA9BCEE4FF01}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
           <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+            <a:picLocks noChangeAspect="1"/>
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
-            <a:extLst>
-              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-              </a:ext>
-            </a:extLst>
-          </a:blip>
-          <a:srcRect/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
         </xdr:blipFill>
-        <xdr:spPr bwMode="auto">
+        <xdr:spPr>
           <a:xfrm>
-            <a:off x="10172700" y="5429250"/>
-            <a:ext cx="2448670" cy="2757600"/>
+            <a:off x="20329071" y="4327072"/>
+            <a:ext cx="2581635" cy="2905530"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
           </a:prstGeom>
-          <a:noFill/>
-          <a:extLst>
-            <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-              <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-                <a:solidFill>
-                  <a:srgbClr val="FFFFFF"/>
-                </a:solidFill>
-              </a14:hiddenFill>
-            </a:ext>
-          </a:extLst>
         </xdr:spPr>
       </xdr:pic>
     </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>530276</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>65315</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>51861</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>46025</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1073" name="Рисунок 1072">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29418562-7147-4C4D-19CB-F38B1C0E9202}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2677064" y="827315"/>
+          <a:ext cx="3566047" cy="552210"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1603,6 +1783,123 @@
           <a:xfrm>
             <a:off x="7962900" y="4533900"/>
             <a:ext cx="2619654" cy="2757600"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>379148</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>105600</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="26" name="Группа 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8DB68E0-0725-49CA-918F-4DE139C9B4B1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="3048000" y="4381500"/>
+          <a:ext cx="2817548" cy="3153600"/>
+          <a:chOff x="20206607" y="4191000"/>
+          <a:chExt cx="2817548" cy="3153600"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="27" name="Прямоугольник: скругленные углы 26">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E246A1D0-CF24-B8E1-26DE-4613C6BC245E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="20206607" y="4191000"/>
+            <a:ext cx="2817548" cy="3153600"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="B766D8"/>
+          </a:solidFill>
+          <a:ln w="38100">
+            <a:solidFill>
+              <a:srgbClr val="68217A"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="ru-RU" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="28" name="Рисунок 27">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84FAE7AD-D303-4001-7CF0-C6C7F2938A31}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="20329071" y="4327072"/>
+            <a:ext cx="2581635" cy="2905530"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -1932,9 +2229,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B23A8047-2F03-426D-940C-C443A7B38389}">
-  <dimension ref="A1"/>
+  <sheetPr codeName="Лист1"/>
+  <dimension ref="A14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" customWidth="1"/>
+    <col min="7" max="7" width="2.5703125" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="14" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -1942,6 +2249,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14FB943F-97A3-4D6F-844A-20BC18394118}">
+  <sheetPr codeName="Лист2"/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/Книга1.xlsx
+++ b/Книга1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Мои документы\JavaScript\Sonata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F52B6B5B-7FF9-47B8-AECD-A97D1B8A0ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51BF9002-7927-43E8-93D2-3C08451973F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7E13A5E9-D6E6-4C53-8805-533BEED830C4}"/>
   </bookViews>
@@ -111,20 +111,20 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>435219</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>109904</xdr:rowOff>
+      <xdr:rowOff>87921</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>176447</xdr:colOff>
+      <xdr:colOff>170757</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>161193</xdr:rowOff>
+      <xdr:rowOff>153865</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1080" name="Прямоугольник: скругленные верхние углы 1079">
+        <xdr:cNvPr id="1081" name="Прямоугольник: скругленные верхние углы 1080">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B25B70EB-60FC-418D-A900-C715146B460C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{387BA21B-09CA-431B-B2AC-CD1E267E9801}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -132,8 +132,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="10800000">
-          <a:off x="2582007" y="1443404"/>
-          <a:ext cx="3785690" cy="2791558"/>
+          <a:off x="2582007" y="1421421"/>
+          <a:ext cx="3780000" cy="2806213"/>
         </a:xfrm>
         <a:prstGeom prst="round2SameRect">
           <a:avLst>
@@ -142,7 +142,9 @@
           </a:avLst>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="303243"/>
+          <a:srgbClr val="303243">
+            <a:alpha val="69804"/>
+          </a:srgbClr>
         </a:solidFill>
         <a:ln w="38100">
           <a:solidFill>
